--- a/data/seed/mentor_subjectwise_final.xlsx
+++ b/data/seed/mentor_subjectwise_final.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vansh\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2d704ffe42a61a63/Desktop/Attendance-Companion/data/seed/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B9E6957-0993-40B9-B94C-2C9CFC6580E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{7B9E6957-0993-40B9-B94C-2C9CFC6580E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8AE29BE-6F15-4121-8A36-E21A7935AB00}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1218,7 +1218,7 @@
         <v>74</v>
       </c>
       <c r="D20">
-        <v>9856789012</v>
+        <v>7827624547</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>47</v>
@@ -1241,7 +1241,7 @@
         <v>74</v>
       </c>
       <c r="D21">
-        <v>9856789012</v>
+        <v>7827624547</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>47</v>

--- a/data/seed/mentor_subjectwise_final.xlsx
+++ b/data/seed/mentor_subjectwise_final.xlsx
@@ -471,6 +471,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
